--- a/model_fitting/2010/model_comparison_final.xlsx
+++ b/model_fitting/2010/model_comparison_final.xlsx
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>693487.8100000001</v>
+        <v>693483.22</v>
       </c>
       <c r="E2" t="n">
-        <v>693786.59</v>
+        <v>693782</v>
       </c>
       <c r="F2" t="n">
-        <v>-346715.91</v>
+        <v>-346713.61</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>885483.4300000001</v>
+        <v>885478.13</v>
       </c>
       <c r="E3" t="n">
-        <v>-3924876.34</v>
+        <v>-3924850.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-442720.71</v>
+        <v>-442718.06</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>367895.55</v>
+        <v>367891.27</v>
       </c>
       <c r="E4" t="n">
-        <v>368119.64</v>
+        <v>368115.35</v>
       </c>
       <c r="F4" t="n">
-        <v>-183926.78</v>
+        <v>-183924.63</v>
       </c>
     </row>
   </sheetData>
